--- a/pregenereated_results/s2/ate_evalue_retention_survival.xlsx
+++ b/pregenereated_results/s2/ate_evalue_retention_survival.xlsx
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5946651297685973</v>
+        <v>0.5868</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5946651297685973</v>
+        <v>0.5868</v>
       </c>
       <c r="E2" t="n">
-        <v>2.752236621379941</v>
+        <v>2.799601818676769</v>
       </c>
       <c r="F2" t="n">
-        <v>1.47884531439044</v>
+        <v>1.489161925919893</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -510,11 +510,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-value = 2.75. An unmeasured confounder would need risk ratio associations of at least 2.75 with both treatment and outcome to explain away this effect. This represents moderate robustness. The E-value for the confidence interval bound is 1.48, meaning a confounder of this strength could shift the CI to include the null.</t>
+          <t>E-value = 2.80. An unmeasured confounder would need risk ratio associations of at least 2.80 with both treatment and outcome to explain away this effect. This represents moderate robustness. The E-value for the confidence interval bound is 1.49, meaning a confounder of this strength could shift the CI to include the null.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.01274825851729578</v>
+        <v>0.0126</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
